--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
   </si>
   <si>
     <t xml:space="preserve">Ce ConceptMap de l'élément PersonneStructure présente trois groupes de mapping: 
- - Mapping 1 : entre le modèle métier \"PersonneStructure\" et l'élément CDA \"relatedEntity\"
+ - Mapping 1 : entre le modèle métier \"FRLMPersonneStructure\" et l'élément CDA \"relatedEntity\"
  - Mapping 2 : entre l'élément CDA \"relatedEntity\" et le profil FHIR \"FrRelatedPersonDocument\"
  - Mapping 3 : entre l'élément CDA \"relatedEntity\" et l'élément FHIR \"Patient.contact\" </t>
   </si>
@@ -107,16 +107,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructure</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-related-entity</t>
-  </si>
-  <si>
-    <t>PersonneStructure</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-related-entity</t>
+  </si>
+  <si>
+    <t>FRLMPersonneStructure</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -125,55 +125,55 @@
     <t>relatedEntity</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.professionRole</t>
+    <t>FRLMPersonneStructure.personne.professionRole</t>
   </si>
   <si>
     <t>relatedEntity@classCode</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.lien</t>
+    <t>FRLMPersonneStructure.personne.lien</t>
   </si>
   <si>
     <t>relatedEntity.code</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.adresse</t>
+    <t>FRLMPersonneStructure.personne.adresse</t>
   </si>
   <si>
     <t>relatedEntity.addr</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.coordonneesTelecom</t>
+    <t>FRLMPersonneStructure.personne.coordonneesTelecom</t>
   </si>
   <si>
     <t>relatedEntity.telecom</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne</t>
   </si>
   <si>
     <t>relatedEntity.relatedPerson</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.nomPersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.nomPersonne</t>
   </si>
   <si>
     <t>relatedEntity.relatedPerson.name.family</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.prenomPersonne</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.prenomPersonne</t>
   </si>
   <si>
     <t>relatedEntity.relatedPerson.name.given</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.civilite</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.civilite</t>
   </si>
   <si>
     <t>relatedEntity.relatedPerson.name.prefix</t>
   </si>
   <si>
-    <t>PersonneStructure.personne.IdentitePersonne.titre</t>
+    <t>FRLMPersonneStructure.personne.IdentitePersonne.titre</t>
   </si>
   <si>
     <t>relatedEntity.relatedPerson.name.suffix</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/main/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
